--- a/public/plantilla-mensual-amb.xlsx
+++ b/public/plantilla-mensual-amb.xlsx
@@ -139,7 +139,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -176,8 +176,13 @@
         <bgColor rgb="FFFFFF66"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="18">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -376,6 +381,64 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00808080"/>
+      </left>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -385,7 +448,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -531,6 +594,21 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2159,7 +2237,7 @@
     <tabColor theme="4" tint="0.3999755851924192"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L54"/>
+  <dimension ref="A1:L65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="12.77734375" customWidth="1" style="34" min="1" max="1"/>
@@ -2278,7 +2356,7 @@
       </c>
       <c r="K8" s="28" t="inlineStr">
         <is>
-          <t>1 de 2</t>
+          <t>1 de 3</t>
         </is>
       </c>
       <c r="L8" s="26" t="n"/>
@@ -3349,23 +3427,223 @@
       <c r="K53" s="29" t="n"/>
       <c r="L53" s="23" t="n"/>
     </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
+    <row r="54" ht="16.5" customHeight="1" s="34">
+      <c r="A54" s="21" t="inlineStr">
+        <is>
+          <t>8. REGISTRO FOTOGRÁFICO</t>
+        </is>
+      </c>
+      <c r="B54" s="22" t="n"/>
+      <c r="C54" s="22" t="n"/>
+      <c r="D54" s="22" t="n"/>
+      <c r="E54" s="22" t="n"/>
+      <c r="F54" s="22" t="n"/>
+      <c r="G54" s="22" t="n"/>
+      <c r="H54" s="22" t="n"/>
+      <c r="I54" s="22" t="n"/>
+      <c r="J54" s="22" t="n"/>
+      <c r="K54" s="22" t="n"/>
+      <c r="L54" s="23" t="n"/>
+    </row>
+    <row r="55" ht="165" customHeight="1" s="34">
+      <c r="A55" s="57" t="n"/>
+      <c r="B55" s="62" t="n"/>
+      <c r="C55" s="62" t="n"/>
+      <c r="D55" s="62" t="n"/>
+      <c r="E55" s="62" t="n"/>
+      <c r="F55" s="63" t="n"/>
+      <c r="G55" s="57" t="n"/>
+      <c r="H55" s="62" t="n"/>
+      <c r="I55" s="62" t="n"/>
+      <c r="J55" s="62" t="n"/>
+      <c r="K55" s="62" t="n"/>
+      <c r="L55" s="63" t="n"/>
+    </row>
+    <row r="56" ht="30" customHeight="1" s="34">
+      <c r="A56" s="59" t="inlineStr">
+        <is>
+          <t>Foto 01</t>
+        </is>
+      </c>
+      <c r="B56" s="63" t="n"/>
+      <c r="C56" s="61" t="n"/>
+      <c r="D56" s="62" t="n"/>
+      <c r="E56" s="62" t="n"/>
+      <c r="F56" s="63" t="n"/>
+      <c r="G56" s="59" t="inlineStr">
+        <is>
+          <t>Foto 02</t>
+        </is>
+      </c>
+      <c r="H56" s="63" t="n"/>
+      <c r="I56" s="61" t="n"/>
+      <c r="J56" s="62" t="n"/>
+      <c r="K56" s="62" t="n"/>
+      <c r="L56" s="63" t="n"/>
+    </row>
+    <row r="57" ht="165" customHeight="1" s="34">
+      <c r="A57" s="57" t="n"/>
+      <c r="B57" s="62" t="n"/>
+      <c r="C57" s="62" t="n"/>
+      <c r="D57" s="62" t="n"/>
+      <c r="E57" s="62" t="n"/>
+      <c r="F57" s="63" t="n"/>
+      <c r="G57" s="57" t="n"/>
+      <c r="H57" s="62" t="n"/>
+      <c r="I57" s="62" t="n"/>
+      <c r="J57" s="62" t="n"/>
+      <c r="K57" s="62" t="n"/>
+      <c r="L57" s="63" t="n"/>
+    </row>
+    <row r="58" ht="30" customHeight="1" s="34">
+      <c r="A58" s="59" t="inlineStr">
+        <is>
+          <t>Foto 03</t>
+        </is>
+      </c>
+      <c r="B58" s="63" t="n"/>
+      <c r="C58" s="61" t="n"/>
+      <c r="D58" s="62" t="n"/>
+      <c r="E58" s="62" t="n"/>
+      <c r="F58" s="63" t="n"/>
+      <c r="G58" s="59" t="inlineStr">
+        <is>
+          <t>Foto 04</t>
+        </is>
+      </c>
+      <c r="H58" s="63" t="n"/>
+      <c r="I58" s="61" t="n"/>
+      <c r="J58" s="62" t="n"/>
+      <c r="K58" s="62" t="n"/>
+      <c r="L58" s="63" t="n"/>
+    </row>
+    <row r="59" ht="165" customHeight="1" s="34">
+      <c r="A59" s="57" t="n"/>
+      <c r="B59" s="62" t="n"/>
+      <c r="C59" s="62" t="n"/>
+      <c r="D59" s="62" t="n"/>
+      <c r="E59" s="62" t="n"/>
+      <c r="F59" s="63" t="n"/>
+      <c r="G59" s="57" t="n"/>
+      <c r="H59" s="62" t="n"/>
+      <c r="I59" s="62" t="n"/>
+      <c r="J59" s="62" t="n"/>
+      <c r="K59" s="62" t="n"/>
+      <c r="L59" s="63" t="n"/>
+    </row>
+    <row r="60" ht="30" customHeight="1" s="34">
+      <c r="A60" s="59" t="inlineStr">
+        <is>
+          <t>Foto 05</t>
+        </is>
+      </c>
+      <c r="B60" s="63" t="n"/>
+      <c r="C60" s="61" t="n"/>
+      <c r="D60" s="62" t="n"/>
+      <c r="E60" s="62" t="n"/>
+      <c r="F60" s="63" t="n"/>
+      <c r="G60" s="59" t="inlineStr">
+        <is>
+          <t>Foto 06</t>
+        </is>
+      </c>
+      <c r="H60" s="63" t="n"/>
+      <c r="I60" s="61" t="n"/>
+      <c r="J60" s="62" t="n"/>
+      <c r="K60" s="62" t="n"/>
+      <c r="L60" s="63" t="n"/>
+    </row>
+    <row r="61" ht="165" customHeight="1" s="34">
+      <c r="A61" s="57" t="n"/>
+      <c r="B61" s="62" t="n"/>
+      <c r="C61" s="62" t="n"/>
+      <c r="D61" s="62" t="n"/>
+      <c r="E61" s="62" t="n"/>
+      <c r="F61" s="63" t="n"/>
+      <c r="G61" s="57" t="n"/>
+      <c r="H61" s="62" t="n"/>
+      <c r="I61" s="62" t="n"/>
+      <c r="J61" s="62" t="n"/>
+      <c r="K61" s="62" t="n"/>
+      <c r="L61" s="63" t="n"/>
+    </row>
+    <row r="62" ht="30" customHeight="1" s="34">
+      <c r="A62" s="59" t="inlineStr">
+        <is>
+          <t>Foto 07</t>
+        </is>
+      </c>
+      <c r="B62" s="63" t="n"/>
+      <c r="C62" s="61" t="n"/>
+      <c r="D62" s="62" t="n"/>
+      <c r="E62" s="62" t="n"/>
+      <c r="F62" s="63" t="n"/>
+      <c r="G62" s="59" t="inlineStr">
+        <is>
+          <t>Foto 08</t>
+        </is>
+      </c>
+      <c r="H62" s="63" t="n"/>
+      <c r="I62" s="61" t="n"/>
+      <c r="J62" s="62" t="n"/>
+      <c r="K62" s="62" t="n"/>
+      <c r="L62" s="63" t="n"/>
+    </row>
+    <row r="63" ht="165" customHeight="1" s="34">
+      <c r="A63" s="57" t="n"/>
+      <c r="B63" s="62" t="n"/>
+      <c r="C63" s="62" t="n"/>
+      <c r="D63" s="62" t="n"/>
+      <c r="E63" s="62" t="n"/>
+      <c r="F63" s="63" t="n"/>
+      <c r="G63" s="57" t="n"/>
+      <c r="H63" s="62" t="n"/>
+      <c r="I63" s="62" t="n"/>
+      <c r="J63" s="62" t="n"/>
+      <c r="K63" s="62" t="n"/>
+      <c r="L63" s="63" t="n"/>
+    </row>
+    <row r="64" ht="30" customHeight="1" s="34">
+      <c r="A64" s="59" t="inlineStr">
+        <is>
+          <t>Foto 09</t>
+        </is>
+      </c>
+      <c r="B64" s="63" t="n"/>
+      <c r="C64" s="61" t="n"/>
+      <c r="D64" s="62" t="n"/>
+      <c r="E64" s="62" t="n"/>
+      <c r="F64" s="63" t="n"/>
+      <c r="G64" s="59" t="inlineStr">
+        <is>
+          <t>Foto 10</t>
+        </is>
+      </c>
+      <c r="H64" s="63" t="n"/>
+      <c r="I64" s="61" t="n"/>
+      <c r="J64" s="62" t="n"/>
+      <c r="K64" s="62" t="n"/>
+      <c r="L64" s="63" t="n"/>
+    </row>
+    <row r="65" s="34">
+      <c r="A65" s="1" t="inlineStr">
         <is>
           <t>REV. 08/10/2026</t>
         </is>
       </c>
-      <c r="G54" s="43">
+      <c r="G65" s="43">
         <f>K5</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="149">
+  <mergeCells count="180">
+    <mergeCell ref="A64:B64"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A37:L37"/>
     <mergeCell ref="K33:L33"/>
-    <mergeCell ref="A37:L37"/>
+    <mergeCell ref="A55:F55"/>
     <mergeCell ref="I26:J26"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B36:E36"/>
@@ -3373,17 +3651,25 @@
     <mergeCell ref="K35:L35"/>
     <mergeCell ref="E51:F51"/>
     <mergeCell ref="D1:L2"/>
+    <mergeCell ref="C62:F62"/>
+    <mergeCell ref="G55:L55"/>
+    <mergeCell ref="A56:B56"/>
     <mergeCell ref="B31:E31"/>
     <mergeCell ref="K52:L52"/>
     <mergeCell ref="G34:H34"/>
+    <mergeCell ref="C64:F64"/>
     <mergeCell ref="D5:I5"/>
     <mergeCell ref="I42:J42"/>
     <mergeCell ref="K42:L42"/>
+    <mergeCell ref="G58:H58"/>
     <mergeCell ref="B39:E39"/>
     <mergeCell ref="I52:J52"/>
     <mergeCell ref="A53:B53"/>
     <mergeCell ref="I44:J44"/>
+    <mergeCell ref="A62:B62"/>
     <mergeCell ref="K53:L53"/>
+    <mergeCell ref="C56:F56"/>
+    <mergeCell ref="I58:L58"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="A49:L49"/>
     <mergeCell ref="B38:E38"/>
@@ -3399,10 +3685,11 @@
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="J24:L24"/>
     <mergeCell ref="K30:L30"/>
+    <mergeCell ref="G57:L57"/>
+    <mergeCell ref="A11:B11"/>
     <mergeCell ref="C48:L48"/>
-    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C14:D14"/>
     <mergeCell ref="B33:E33"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="E14:F14"/>
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B41:E41"/>
@@ -3414,48 +3701,59 @@
     <mergeCell ref="A32:L32"/>
     <mergeCell ref="A46:B46"/>
     <mergeCell ref="K41:L41"/>
+    <mergeCell ref="G62:H62"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="I43:J43"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="K43:L43"/>
     <mergeCell ref="C12:G12"/>
     <mergeCell ref="G33:H33"/>
+    <mergeCell ref="I33:J33"/>
     <mergeCell ref="B19:F19"/>
-    <mergeCell ref="I33:J33"/>
     <mergeCell ref="K27:L27"/>
     <mergeCell ref="G26:H26"/>
+    <mergeCell ref="A59:F59"/>
     <mergeCell ref="G35:H35"/>
+    <mergeCell ref="I35:J35"/>
     <mergeCell ref="H12:I12"/>
-    <mergeCell ref="I35:J35"/>
     <mergeCell ref="A52:B52"/>
+    <mergeCell ref="I56:L56"/>
     <mergeCell ref="B29:E29"/>
+    <mergeCell ref="A61:F61"/>
+    <mergeCell ref="G60:H60"/>
+    <mergeCell ref="K6:L6"/>
     <mergeCell ref="C53:D53"/>
-    <mergeCell ref="K6:L6"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="A25:L25"/>
     <mergeCell ref="G42:H42"/>
     <mergeCell ref="K5:L5"/>
+    <mergeCell ref="E52:F52"/>
     <mergeCell ref="J4:L4"/>
-    <mergeCell ref="E52:F52"/>
     <mergeCell ref="G39:H39"/>
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="K29:L29"/>
+    <mergeCell ref="I60:L60"/>
+    <mergeCell ref="G65:L65"/>
     <mergeCell ref="E50:H50"/>
     <mergeCell ref="K44:L44"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="E13:F13"/>
     <mergeCell ref="D3:L3"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="B23:F23"/>
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="K31:L31"/>
     <mergeCell ref="K40:L40"/>
+    <mergeCell ref="C58:F58"/>
     <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="J18:L18"/>
     <mergeCell ref="K8:L8"/>
-    <mergeCell ref="J18:L18"/>
-    <mergeCell ref="B43:E43"/>
     <mergeCell ref="C51:D51"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="J17:L17"/>
     <mergeCell ref="B42:E42"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="G59:L59"/>
     <mergeCell ref="G51:H51"/>
     <mergeCell ref="K7:L7"/>
     <mergeCell ref="A15:L15"/>
@@ -3463,20 +3761,28 @@
     <mergeCell ref="J19:L19"/>
     <mergeCell ref="B44:E44"/>
     <mergeCell ref="G41:H41"/>
+    <mergeCell ref="G61:L61"/>
+    <mergeCell ref="I62:L62"/>
     <mergeCell ref="B34:E34"/>
     <mergeCell ref="B28:E28"/>
+    <mergeCell ref="C60:F60"/>
+    <mergeCell ref="G56:H56"/>
+    <mergeCell ref="A54:L54"/>
     <mergeCell ref="I34:J34"/>
     <mergeCell ref="G43:H43"/>
     <mergeCell ref="K34:L34"/>
     <mergeCell ref="G52:H52"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="I64:L64"/>
     <mergeCell ref="B30:E30"/>
     <mergeCell ref="G27:H27"/>
     <mergeCell ref="I27:J27"/>
     <mergeCell ref="G36:H36"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="J20:L20"/>
     <mergeCell ref="B22:F22"/>
-    <mergeCell ref="J20:L20"/>
-    <mergeCell ref="I36:J36"/>
     <mergeCell ref="K36:L36"/>
+    <mergeCell ref="A57:F57"/>
     <mergeCell ref="I50:L50"/>
     <mergeCell ref="J22:L22"/>
     <mergeCell ref="G53:H53"/>
@@ -3485,25 +3791,25 @@
     <mergeCell ref="I28:J28"/>
     <mergeCell ref="J12:L12"/>
     <mergeCell ref="J21:L21"/>
-    <mergeCell ref="G54:L54"/>
+    <mergeCell ref="G63:L63"/>
     <mergeCell ref="A10:L10"/>
     <mergeCell ref="G30:H30"/>
     <mergeCell ref="A47:B47"/>
     <mergeCell ref="J23:L23"/>
     <mergeCell ref="G14:H14"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="A9:L9"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="C47:L47"/>
     <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="A9:L9"/>
-    <mergeCell ref="C47:L47"/>
-    <mergeCell ref="C52:D52"/>
     <mergeCell ref="K39:L39"/>
     <mergeCell ref="K14:L14"/>
     <mergeCell ref="G29:H29"/>
     <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I38:J38"/>
     <mergeCell ref="B24:F24"/>
-    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="A50:D50"/>
     <mergeCell ref="K38:L38"/>
-    <mergeCell ref="A50:D50"/>
     <mergeCell ref="A45:L45"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="G31:H31"/>
@@ -3511,6 +3817,7 @@
     <mergeCell ref="I31:J31"/>
     <mergeCell ref="G40:H40"/>
     <mergeCell ref="I40:J40"/>
+    <mergeCell ref="A58:B58"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.7" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
@@ -3522,8 +3829,9 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <rowBreaks count="1" manualBreakCount="1">
+  <rowBreaks count="2" manualBreakCount="2">
     <brk id="31" min="0" max="16383" man="1"/>
+    <brk id="53" min="0" max="16383" man="1"/>
   </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>

--- a/public/plantilla-mensual-amb.xlsx
+++ b/public/plantilla-mensual-amb.xlsx
@@ -15,6 +15,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="#,##0.##"/>
+  </numFmts>
   <fonts count="17">
     <font>
       <name val="Calibri"/>

--- a/public/plantilla-mensual-amb.xlsx
+++ b/public/plantilla-mensual-amb.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="3" autoFilterDateGrouping="1"/>
+    <workbookView activeTab="0" visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Informe Mensual Ambiental" sheetId="1" state="visible" r:id="rId1"/>

--- a/public/plantilla-mensual-amb.xlsx
+++ b/public/plantilla-mensual-amb.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView activeTab="0" visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Informe Mensual Ambiental" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,9 +16,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="#,##0.##"/>
+    <numFmt numFmtId="164" formatCode="#,##0.##"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -140,6 +140,15 @@
       <family val="2"/>
       <b val="1"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="8">
@@ -451,7 +460,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -491,7 +500,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="16" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -570,7 +579,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -585,7 +594,7 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -612,6 +621,68 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="17" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="18" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1896,6 +1967,74 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -2245,6 +2384,7 @@
   <cols>
     <col width="12.77734375" customWidth="1" style="34" min="1" max="1"/>
     <col width="13" customWidth="1" style="34" min="2" max="3"/>
+    <col width="13" customWidth="1" style="34" min="3" max="3"/>
     <col width="15.77734375" customWidth="1" style="34" min="4" max="4"/>
     <col width="10" customWidth="1" style="34" min="5" max="5"/>
     <col width="15.77734375" customWidth="1" style="34" min="6" max="10"/>
@@ -2407,16 +2547,16 @@
         </is>
       </c>
       <c r="B11" s="26" t="n"/>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="25" t="n"/>
-      <c r="E11" s="25" t="n"/>
-      <c r="F11" s="25" t="n"/>
-      <c r="G11" s="25" t="n"/>
-      <c r="H11" s="25" t="n"/>
-      <c r="I11" s="25" t="n"/>
-      <c r="J11" s="25" t="n"/>
-      <c r="K11" s="25" t="n"/>
-      <c r="L11" s="26" t="n"/>
+      <c r="C11" s="64" t="n"/>
+      <c r="D11" s="65" t="n"/>
+      <c r="E11" s="65" t="n"/>
+      <c r="F11" s="65" t="n"/>
+      <c r="G11" s="65" t="n"/>
+      <c r="H11" s="65" t="n"/>
+      <c r="I11" s="65" t="n"/>
+      <c r="J11" s="65" t="n"/>
+      <c r="K11" s="65" t="n"/>
+      <c r="L11" s="66" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1" s="34">
       <c r="A12" s="27" t="inlineStr">
@@ -2425,20 +2565,20 @@
         </is>
       </c>
       <c r="B12" s="26" t="n"/>
-      <c r="C12" s="24" t="n"/>
-      <c r="D12" s="25" t="n"/>
-      <c r="E12" s="25" t="n"/>
-      <c r="F12" s="25" t="n"/>
-      <c r="G12" s="26" t="n"/>
+      <c r="C12" s="64" t="n"/>
+      <c r="D12" s="65" t="n"/>
+      <c r="E12" s="65" t="n"/>
+      <c r="F12" s="65" t="n"/>
+      <c r="G12" s="66" t="n"/>
       <c r="H12" s="27" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
       <c r="I12" s="26" t="n"/>
-      <c r="J12" s="24" t="n"/>
-      <c r="K12" s="25" t="n"/>
-      <c r="L12" s="26" t="n"/>
+      <c r="J12" s="64" t="n"/>
+      <c r="K12" s="65" t="n"/>
+      <c r="L12" s="66" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1" s="34">
       <c r="A13" s="27" t="inlineStr">
@@ -2447,24 +2587,24 @@
         </is>
       </c>
       <c r="B13" s="26" t="n"/>
-      <c r="C13" s="49" t="n"/>
-      <c r="D13" s="26" t="n"/>
+      <c r="C13" s="67" t="n"/>
+      <c r="D13" s="66" t="n"/>
       <c r="E13" s="27" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
       </c>
       <c r="F13" s="26" t="n"/>
-      <c r="G13" s="49" t="n"/>
-      <c r="H13" s="26" t="n"/>
+      <c r="G13" s="67" t="n"/>
+      <c r="H13" s="66" t="n"/>
       <c r="I13" s="27" t="inlineStr">
         <is>
           <t>Informe N°</t>
         </is>
       </c>
       <c r="J13" s="26" t="n"/>
-      <c r="K13" s="49" t="n"/>
-      <c r="L13" s="26" t="n"/>
+      <c r="K13" s="67" t="n"/>
+      <c r="L13" s="66" t="n"/>
     </row>
     <row r="14" ht="21" customHeight="1" s="34">
       <c r="A14" s="27" t="inlineStr">
@@ -2473,24 +2613,24 @@
         </is>
       </c>
       <c r="B14" s="26" t="n"/>
-      <c r="C14" s="49" t="n"/>
-      <c r="D14" s="26" t="n"/>
+      <c r="C14" s="67" t="n"/>
+      <c r="D14" s="66" t="n"/>
       <c r="E14" s="27" t="inlineStr">
         <is>
           <t>Días trabajados</t>
         </is>
       </c>
       <c r="F14" s="26" t="n"/>
-      <c r="G14" s="49" t="n"/>
-      <c r="H14" s="26" t="n"/>
+      <c r="G14" s="67" t="n"/>
+      <c r="H14" s="66" t="n"/>
       <c r="I14" s="27" t="inlineStr">
         <is>
           <t>% avance de obra</t>
         </is>
       </c>
       <c r="J14" s="26" t="n"/>
-      <c r="K14" s="52" t="n"/>
-      <c r="L14" s="26" t="n"/>
+      <c r="K14" s="68" t="n"/>
+      <c r="L14" s="66" t="n"/>
     </row>
     <row r="15" ht="16.5" customHeight="1" s="34">
       <c r="A15" s="21" t="inlineStr">
@@ -2549,10 +2689,10 @@
       <c r="L16" s="20" t="n"/>
     </row>
     <row r="17" ht="19.95" customHeight="1" s="34">
-      <c r="A17" s="55" t="n">
+      <c r="A17" s="69" t="n">
         <v>1</v>
       </c>
-      <c r="B17" s="47" t="inlineStr">
+      <c r="B17" s="70" t="inlineStr">
         <is>
           <t>Inspecciones ambientales de obra</t>
         </is>
@@ -2561,21 +2701,21 @@
       <c r="D17" s="22" t="n"/>
       <c r="E17" s="22" t="n"/>
       <c r="F17" s="23" t="n"/>
-      <c r="G17" s="55" t="n"/>
-      <c r="H17" s="55" t="n"/>
-      <c r="I17" s="16">
+      <c r="G17" s="71" t="n"/>
+      <c r="H17" s="71" t="n"/>
+      <c r="I17" s="72">
         <f>IF(OR(G17="",G17=0,H17=""),"",H17/G17)</f>
         <v/>
       </c>
-      <c r="J17" s="47" t="n"/>
-      <c r="K17" s="22" t="n"/>
-      <c r="L17" s="23" t="n"/>
+      <c r="J17" s="73" t="n"/>
+      <c r="K17" s="74" t="n"/>
+      <c r="L17" s="75" t="n"/>
     </row>
     <row r="18" ht="19.95" customHeight="1" s="34">
-      <c r="A18" s="55" t="n">
+      <c r="A18" s="69" t="n">
         <v>2</v>
       </c>
-      <c r="B18" s="47" t="inlineStr">
+      <c r="B18" s="70" t="inlineStr">
         <is>
           <t>Charlas y capacitaciones ambientales</t>
         </is>
@@ -2584,21 +2724,21 @@
       <c r="D18" s="22" t="n"/>
       <c r="E18" s="22" t="n"/>
       <c r="F18" s="23" t="n"/>
-      <c r="G18" s="55" t="n"/>
-      <c r="H18" s="55" t="n"/>
-      <c r="I18" s="16">
+      <c r="G18" s="71" t="n"/>
+      <c r="H18" s="71" t="n"/>
+      <c r="I18" s="72">
         <f>IF(OR(G18="",G18=0,H18=""),"",H18/G18)</f>
         <v/>
       </c>
-      <c r="J18" s="47" t="n"/>
-      <c r="K18" s="22" t="n"/>
-      <c r="L18" s="23" t="n"/>
+      <c r="J18" s="73" t="n"/>
+      <c r="K18" s="74" t="n"/>
+      <c r="L18" s="75" t="n"/>
     </row>
     <row r="19" ht="19.95" customHeight="1" s="34">
-      <c r="A19" s="55" t="n">
+      <c r="A19" s="69" t="n">
         <v>3</v>
       </c>
-      <c r="B19" s="47" t="inlineStr">
+      <c r="B19" s="70" t="inlineStr">
         <is>
           <t>Entrega de residuos a gestores autorizados</t>
         </is>
@@ -2607,21 +2747,21 @@
       <c r="D19" s="22" t="n"/>
       <c r="E19" s="22" t="n"/>
       <c r="F19" s="23" t="n"/>
-      <c r="G19" s="55" t="n"/>
-      <c r="H19" s="55" t="n"/>
-      <c r="I19" s="16">
+      <c r="G19" s="71" t="n"/>
+      <c r="H19" s="71" t="n"/>
+      <c r="I19" s="72">
         <f>IF(OR(G19="",G19=0,H19=""),"",H19/G19)</f>
         <v/>
       </c>
-      <c r="J19" s="47" t="n"/>
-      <c r="K19" s="22" t="n"/>
-      <c r="L19" s="23" t="n"/>
+      <c r="J19" s="73" t="n"/>
+      <c r="K19" s="74" t="n"/>
+      <c r="L19" s="75" t="n"/>
     </row>
     <row r="20" ht="19.95" customHeight="1" s="34">
-      <c r="A20" s="55" t="n">
+      <c r="A20" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="B20" s="47" t="inlineStr">
+      <c r="B20" s="70" t="inlineStr">
         <is>
           <t>Monitoreos o mediciones (ruido, material particulado, agua)</t>
         </is>
@@ -2630,21 +2770,21 @@
       <c r="D20" s="22" t="n"/>
       <c r="E20" s="22" t="n"/>
       <c r="F20" s="23" t="n"/>
-      <c r="G20" s="55" t="n"/>
-      <c r="H20" s="55" t="n"/>
-      <c r="I20" s="16">
+      <c r="G20" s="71" t="n"/>
+      <c r="H20" s="71" t="n"/>
+      <c r="I20" s="72">
         <f>IF(OR(G20="",G20=0,H20=""),"",H20/G20)</f>
         <v/>
       </c>
-      <c r="J20" s="47" t="n"/>
-      <c r="K20" s="22" t="n"/>
-      <c r="L20" s="23" t="n"/>
+      <c r="J20" s="73" t="n"/>
+      <c r="K20" s="74" t="n"/>
+      <c r="L20" s="75" t="n"/>
     </row>
     <row r="21" ht="19.95" customHeight="1" s="34">
-      <c r="A21" s="55" t="n">
+      <c r="A21" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="B21" s="47" t="inlineStr">
+      <c r="B21" s="70" t="inlineStr">
         <is>
           <t>Mantenimiento de maquinaria y equipos</t>
         </is>
@@ -2653,21 +2793,21 @@
       <c r="D21" s="22" t="n"/>
       <c r="E21" s="22" t="n"/>
       <c r="F21" s="23" t="n"/>
-      <c r="G21" s="55" t="n"/>
-      <c r="H21" s="55" t="n"/>
-      <c r="I21" s="16">
+      <c r="G21" s="71" t="n"/>
+      <c r="H21" s="71" t="n"/>
+      <c r="I21" s="72">
         <f>IF(OR(G21="",G21=0,H21=""),"",H21/G21)</f>
         <v/>
       </c>
-      <c r="J21" s="47" t="n"/>
-      <c r="K21" s="22" t="n"/>
-      <c r="L21" s="23" t="n"/>
+      <c r="J21" s="73" t="n"/>
+      <c r="K21" s="74" t="n"/>
+      <c r="L21" s="75" t="n"/>
     </row>
     <row r="22" ht="19.95" customHeight="1" s="34">
-      <c r="A22" s="55" t="n">
+      <c r="A22" s="69" t="n">
         <v>6</v>
       </c>
-      <c r="B22" s="47" t="inlineStr">
+      <c r="B22" s="70" t="inlineStr">
         <is>
           <t>Inspección de sustancias químicas y combustibles</t>
         </is>
@@ -2676,21 +2816,21 @@
       <c r="D22" s="22" t="n"/>
       <c r="E22" s="22" t="n"/>
       <c r="F22" s="23" t="n"/>
-      <c r="G22" s="55" t="n"/>
-      <c r="H22" s="55" t="n"/>
-      <c r="I22" s="16">
+      <c r="G22" s="71" t="n"/>
+      <c r="H22" s="71" t="n"/>
+      <c r="I22" s="72">
         <f>IF(OR(G22="",G22=0,H22=""),"",H22/G22)</f>
         <v/>
       </c>
-      <c r="J22" s="47" t="n"/>
-      <c r="K22" s="22" t="n"/>
-      <c r="L22" s="23" t="n"/>
+      <c r="J22" s="73" t="n"/>
+      <c r="K22" s="74" t="n"/>
+      <c r="L22" s="75" t="n"/>
     </row>
     <row r="23" ht="19.95" customHeight="1" s="34">
-      <c r="A23" s="55" t="n">
+      <c r="A23" s="69" t="n">
         <v>7</v>
       </c>
-      <c r="B23" s="47" t="inlineStr">
+      <c r="B23" s="70" t="inlineStr">
         <is>
           <t>Seguimiento a contratistas</t>
         </is>
@@ -2699,21 +2839,21 @@
       <c r="D23" s="22" t="n"/>
       <c r="E23" s="22" t="n"/>
       <c r="F23" s="23" t="n"/>
-      <c r="G23" s="55" t="n"/>
-      <c r="H23" s="55" t="n"/>
-      <c r="I23" s="16">
+      <c r="G23" s="71" t="n"/>
+      <c r="H23" s="71" t="n"/>
+      <c r="I23" s="72">
         <f>IF(OR(G23="",G23=0,H23=""),"",H23/G23)</f>
         <v/>
       </c>
-      <c r="J23" s="47" t="n"/>
-      <c r="K23" s="22" t="n"/>
-      <c r="L23" s="23" t="n"/>
+      <c r="J23" s="73" t="n"/>
+      <c r="K23" s="74" t="n"/>
+      <c r="L23" s="75" t="n"/>
     </row>
     <row r="24" ht="19.95" customHeight="1" s="34">
-      <c r="A24" s="55" t="n">
+      <c r="A24" s="69" t="n">
         <v>8</v>
       </c>
-      <c r="B24" s="47" t="inlineStr">
+      <c r="B24" s="70" t="inlineStr">
         <is>
           <t>Acciones correctivas cerradas</t>
         </is>
@@ -2722,15 +2862,15 @@
       <c r="D24" s="22" t="n"/>
       <c r="E24" s="22" t="n"/>
       <c r="F24" s="23" t="n"/>
-      <c r="G24" s="55" t="n"/>
-      <c r="H24" s="55" t="n"/>
-      <c r="I24" s="16">
+      <c r="G24" s="71" t="n"/>
+      <c r="H24" s="71" t="n"/>
+      <c r="I24" s="72">
         <f>IF(OR(G24="",G24=0,H24=""),"",H24/G24)</f>
         <v/>
       </c>
-      <c r="J24" s="47" t="n"/>
-      <c r="K24" s="22" t="n"/>
-      <c r="L24" s="23" t="n"/>
+      <c r="J24" s="73" t="n"/>
+      <c r="K24" s="74" t="n"/>
+      <c r="L24" s="75" t="n"/>
     </row>
     <row r="25" ht="16.5" customHeight="1" s="34">
       <c r="A25" s="21" t="inlineStr">
@@ -2789,10 +2929,10 @@
       <c r="L26" s="20" t="n"/>
     </row>
     <row r="27" ht="19.95" customHeight="1" s="34">
-      <c r="A27" s="55" t="n">
+      <c r="A27" s="69" t="n">
         <v>1</v>
       </c>
-      <c r="B27" s="47" t="inlineStr">
+      <c r="B27" s="70" t="inlineStr">
         <is>
           <t>Residuos ordinarios</t>
         </is>
@@ -2800,23 +2940,23 @@
       <c r="C27" s="22" t="n"/>
       <c r="D27" s="22" t="n"/>
       <c r="E27" s="23" t="n"/>
-      <c r="F27" s="55" t="inlineStr">
+      <c r="F27" s="69" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="G27" s="48" t="n"/>
-      <c r="H27" s="23" t="n"/>
-      <c r="I27" s="48" t="n"/>
-      <c r="J27" s="23" t="n"/>
-      <c r="K27" s="47" t="n"/>
-      <c r="L27" s="23" t="n"/>
+      <c r="G27" s="76" t="n"/>
+      <c r="H27" s="75" t="n"/>
+      <c r="I27" s="76" t="n"/>
+      <c r="J27" s="75" t="n"/>
+      <c r="K27" s="73" t="n"/>
+      <c r="L27" s="75" t="n"/>
     </row>
     <row r="28" ht="19.95" customHeight="1" s="34">
-      <c r="A28" s="55" t="n">
+      <c r="A28" s="69" t="n">
         <v>2</v>
       </c>
-      <c r="B28" s="47" t="inlineStr">
+      <c r="B28" s="70" t="inlineStr">
         <is>
           <t>Residuos aprovechables (reciclables)</t>
         </is>
@@ -2824,23 +2964,23 @@
       <c r="C28" s="22" t="n"/>
       <c r="D28" s="22" t="n"/>
       <c r="E28" s="23" t="n"/>
-      <c r="F28" s="55" t="inlineStr">
+      <c r="F28" s="69" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="G28" s="48" t="n"/>
-      <c r="H28" s="23" t="n"/>
-      <c r="I28" s="48" t="n"/>
-      <c r="J28" s="23" t="n"/>
-      <c r="K28" s="47" t="n"/>
-      <c r="L28" s="23" t="n"/>
+      <c r="G28" s="76" t="n"/>
+      <c r="H28" s="75" t="n"/>
+      <c r="I28" s="76" t="n"/>
+      <c r="J28" s="75" t="n"/>
+      <c r="K28" s="73" t="n"/>
+      <c r="L28" s="75" t="n"/>
     </row>
     <row r="29" ht="19.95" customHeight="1" s="34">
-      <c r="A29" s="55" t="n">
+      <c r="A29" s="69" t="n">
         <v>3</v>
       </c>
-      <c r="B29" s="47" t="inlineStr">
+      <c r="B29" s="70" t="inlineStr">
         <is>
           <t>Residuos de construcción y demolición (RCD)</t>
         </is>
@@ -2848,23 +2988,23 @@
       <c r="C29" s="22" t="n"/>
       <c r="D29" s="22" t="n"/>
       <c r="E29" s="23" t="n"/>
-      <c r="F29" s="55" t="inlineStr">
+      <c r="F29" s="69" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="G29" s="48" t="n"/>
-      <c r="H29" s="23" t="n"/>
-      <c r="I29" s="48" t="n"/>
-      <c r="J29" s="23" t="n"/>
-      <c r="K29" s="47" t="n"/>
-      <c r="L29" s="23" t="n"/>
+      <c r="G29" s="76" t="n"/>
+      <c r="H29" s="75" t="n"/>
+      <c r="I29" s="76" t="n"/>
+      <c r="J29" s="75" t="n"/>
+      <c r="K29" s="73" t="n"/>
+      <c r="L29" s="75" t="n"/>
     </row>
     <row r="30" ht="19.95" customHeight="1" s="34">
-      <c r="A30" s="55" t="n">
+      <c r="A30" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="B30" s="47" t="inlineStr">
+      <c r="B30" s="70" t="inlineStr">
         <is>
           <t>Residuos peligrosos (RESPEL)</t>
         </is>
@@ -2872,23 +3012,23 @@
       <c r="C30" s="22" t="n"/>
       <c r="D30" s="22" t="n"/>
       <c r="E30" s="23" t="n"/>
-      <c r="F30" s="55" t="inlineStr">
+      <c r="F30" s="69" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="G30" s="48" t="n"/>
-      <c r="H30" s="23" t="n"/>
-      <c r="I30" s="48" t="n"/>
-      <c r="J30" s="23" t="n"/>
-      <c r="K30" s="47" t="n"/>
-      <c r="L30" s="23" t="n"/>
+      <c r="G30" s="76" t="n"/>
+      <c r="H30" s="75" t="n"/>
+      <c r="I30" s="76" t="n"/>
+      <c r="J30" s="75" t="n"/>
+      <c r="K30" s="73" t="n"/>
+      <c r="L30" s="75" t="n"/>
     </row>
     <row r="31" ht="19.95" customHeight="1" s="34">
-      <c r="A31" s="55" t="n">
+      <c r="A31" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="B31" s="47" t="inlineStr">
+      <c r="B31" s="70" t="inlineStr">
         <is>
           <t>Residuos orgánicos / vegetales</t>
         </is>
@@ -2896,17 +3036,17 @@
       <c r="C31" s="22" t="n"/>
       <c r="D31" s="22" t="n"/>
       <c r="E31" s="23" t="n"/>
-      <c r="F31" s="55" t="inlineStr">
+      <c r="F31" s="69" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="G31" s="48" t="n"/>
-      <c r="H31" s="23" t="n"/>
-      <c r="I31" s="48" t="n"/>
-      <c r="J31" s="23" t="n"/>
-      <c r="K31" s="47" t="n"/>
-      <c r="L31" s="23" t="n"/>
+      <c r="G31" s="76" t="n"/>
+      <c r="H31" s="75" t="n"/>
+      <c r="I31" s="76" t="n"/>
+      <c r="J31" s="75" t="n"/>
+      <c r="K31" s="73" t="n"/>
+      <c r="L31" s="75" t="n"/>
     </row>
     <row r="32" ht="16.5" customHeight="1" s="34">
       <c r="A32" s="21" t="inlineStr">
@@ -2965,10 +3105,10 @@
       <c r="L33" s="20" t="n"/>
     </row>
     <row r="34" ht="19.95" customHeight="1" s="34">
-      <c r="A34" s="55" t="n">
+      <c r="A34" s="69" t="n">
         <v>1</v>
       </c>
-      <c r="B34" s="47" t="inlineStr">
+      <c r="B34" s="70" t="inlineStr">
         <is>
           <t>Agua</t>
         </is>
@@ -2976,23 +3116,23 @@
       <c r="C34" s="22" t="n"/>
       <c r="D34" s="22" t="n"/>
       <c r="E34" s="23" t="n"/>
-      <c r="F34" s="55" t="inlineStr">
+      <c r="F34" s="69" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="G34" s="48" t="n"/>
-      <c r="H34" s="23" t="n"/>
-      <c r="I34" s="48" t="n"/>
-      <c r="J34" s="23" t="n"/>
-      <c r="K34" s="47" t="n"/>
-      <c r="L34" s="23" t="n"/>
+      <c r="G34" s="76" t="n"/>
+      <c r="H34" s="75" t="n"/>
+      <c r="I34" s="76" t="n"/>
+      <c r="J34" s="75" t="n"/>
+      <c r="K34" s="73" t="n"/>
+      <c r="L34" s="75" t="n"/>
     </row>
     <row r="35" ht="19.95" customHeight="1" s="34">
-      <c r="A35" s="55" t="n">
+      <c r="A35" s="69" t="n">
         <v>2</v>
       </c>
-      <c r="B35" s="47" t="inlineStr">
+      <c r="B35" s="70" t="inlineStr">
         <is>
           <t>Energía eléctrica</t>
         </is>
@@ -3000,23 +3140,23 @@
       <c r="C35" s="22" t="n"/>
       <c r="D35" s="22" t="n"/>
       <c r="E35" s="23" t="n"/>
-      <c r="F35" s="55" t="inlineStr">
+      <c r="F35" s="69" t="inlineStr">
         <is>
           <t>kWh</t>
         </is>
       </c>
-      <c r="G35" s="48" t="n"/>
-      <c r="H35" s="23" t="n"/>
-      <c r="I35" s="48" t="n"/>
-      <c r="J35" s="23" t="n"/>
-      <c r="K35" s="47" t="n"/>
-      <c r="L35" s="23" t="n"/>
+      <c r="G35" s="76" t="n"/>
+      <c r="H35" s="75" t="n"/>
+      <c r="I35" s="76" t="n"/>
+      <c r="J35" s="75" t="n"/>
+      <c r="K35" s="73" t="n"/>
+      <c r="L35" s="75" t="n"/>
     </row>
     <row r="36" ht="19.95" customHeight="1" s="34">
-      <c r="A36" s="55" t="n">
+      <c r="A36" s="69" t="n">
         <v>3</v>
       </c>
-      <c r="B36" s="47" t="inlineStr">
+      <c r="B36" s="70" t="inlineStr">
         <is>
           <t>Combustible (ACPM y gasolina)</t>
         </is>
@@ -3024,17 +3164,17 @@
       <c r="C36" s="22" t="n"/>
       <c r="D36" s="22" t="n"/>
       <c r="E36" s="23" t="n"/>
-      <c r="F36" s="55" t="inlineStr">
+      <c r="F36" s="69" t="inlineStr">
         <is>
           <t>gal</t>
         </is>
       </c>
-      <c r="G36" s="48" t="n"/>
-      <c r="H36" s="23" t="n"/>
-      <c r="I36" s="48" t="n"/>
-      <c r="J36" s="23" t="n"/>
-      <c r="K36" s="47" t="n"/>
-      <c r="L36" s="23" t="n"/>
+      <c r="G36" s="76" t="n"/>
+      <c r="H36" s="75" t="n"/>
+      <c r="I36" s="76" t="n"/>
+      <c r="J36" s="75" t="n"/>
+      <c r="K36" s="73" t="n"/>
+      <c r="L36" s="75" t="n"/>
     </row>
     <row r="37" ht="16.5" customHeight="1" s="34">
       <c r="A37" s="21" t="inlineStr">
@@ -3093,10 +3233,10 @@
       <c r="L38" s="20" t="n"/>
     </row>
     <row r="39" ht="19.95" customHeight="1" s="34">
-      <c r="A39" s="55" t="n">
+      <c r="A39" s="69" t="n">
         <v>1</v>
       </c>
-      <c r="B39" s="47" t="inlineStr">
+      <c r="B39" s="77" t="inlineStr">
         <is>
           <t>Incidentes ambientales</t>
         </is>
@@ -3104,23 +3244,23 @@
       <c r="C39" s="22" t="n"/>
       <c r="D39" s="22" t="n"/>
       <c r="E39" s="23" t="n"/>
-      <c r="F39" s="55" t="inlineStr">
+      <c r="F39" s="69" t="inlineStr">
         <is>
           <t>N°</t>
         </is>
       </c>
-      <c r="G39" s="48" t="n"/>
-      <c r="H39" s="23" t="n"/>
-      <c r="I39" s="48" t="n"/>
-      <c r="J39" s="23" t="n"/>
-      <c r="K39" s="47" t="n"/>
-      <c r="L39" s="23" t="n"/>
+      <c r="G39" s="76" t="n"/>
+      <c r="H39" s="75" t="n"/>
+      <c r="I39" s="76" t="n"/>
+      <c r="J39" s="75" t="n"/>
+      <c r="K39" s="73" t="n"/>
+      <c r="L39" s="75" t="n"/>
     </row>
     <row r="40" ht="19.95" customHeight="1" s="34">
-      <c r="A40" s="55" t="n">
+      <c r="A40" s="69" t="n">
         <v>2</v>
       </c>
-      <c r="B40" s="47" t="inlineStr">
+      <c r="B40" s="77" t="inlineStr">
         <is>
           <t>Quejas de la comunidad recibidas</t>
         </is>
@@ -3128,23 +3268,23 @@
       <c r="C40" s="22" t="n"/>
       <c r="D40" s="22" t="n"/>
       <c r="E40" s="23" t="n"/>
-      <c r="F40" s="55" t="inlineStr">
+      <c r="F40" s="69" t="inlineStr">
         <is>
           <t>N°</t>
         </is>
       </c>
-      <c r="G40" s="48" t="n"/>
-      <c r="H40" s="23" t="n"/>
-      <c r="I40" s="48" t="n"/>
-      <c r="J40" s="23" t="n"/>
-      <c r="K40" s="47" t="n"/>
-      <c r="L40" s="23" t="n"/>
+      <c r="G40" s="76" t="n"/>
+      <c r="H40" s="75" t="n"/>
+      <c r="I40" s="76" t="n"/>
+      <c r="J40" s="75" t="n"/>
+      <c r="K40" s="73" t="n"/>
+      <c r="L40" s="75" t="n"/>
     </row>
     <row r="41" ht="19.95" customHeight="1" s="34">
-      <c r="A41" s="55" t="n">
+      <c r="A41" s="69" t="n">
         <v>3</v>
       </c>
-      <c r="B41" s="47" t="inlineStr">
+      <c r="B41" s="77" t="inlineStr">
         <is>
           <t>Quejas atendidas</t>
         </is>
@@ -3152,23 +3292,23 @@
       <c r="C41" s="22" t="n"/>
       <c r="D41" s="22" t="n"/>
       <c r="E41" s="23" t="n"/>
-      <c r="F41" s="55" t="inlineStr">
+      <c r="F41" s="69" t="inlineStr">
         <is>
           <t>N°</t>
         </is>
       </c>
-      <c r="G41" s="48" t="n"/>
-      <c r="H41" s="23" t="n"/>
-      <c r="I41" s="48" t="n"/>
-      <c r="J41" s="23" t="n"/>
-      <c r="K41" s="47" t="n"/>
-      <c r="L41" s="23" t="n"/>
+      <c r="G41" s="76" t="n"/>
+      <c r="H41" s="75" t="n"/>
+      <c r="I41" s="76" t="n"/>
+      <c r="J41" s="75" t="n"/>
+      <c r="K41" s="73" t="n"/>
+      <c r="L41" s="75" t="n"/>
     </row>
     <row r="42" ht="19.95" customHeight="1" s="34">
-      <c r="A42" s="55" t="n">
+      <c r="A42" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="B42" s="47" t="inlineStr">
+      <c r="B42" s="77" t="inlineStr">
         <is>
           <t>Acciones correctivas abiertas al cierre</t>
         </is>
@@ -3176,23 +3316,23 @@
       <c r="C42" s="22" t="n"/>
       <c r="D42" s="22" t="n"/>
       <c r="E42" s="23" t="n"/>
-      <c r="F42" s="55" t="inlineStr">
+      <c r="F42" s="69" t="inlineStr">
         <is>
           <t>N°</t>
         </is>
       </c>
-      <c r="G42" s="48" t="n"/>
-      <c r="H42" s="23" t="n"/>
-      <c r="I42" s="48" t="n"/>
-      <c r="J42" s="23" t="n"/>
-      <c r="K42" s="47" t="n"/>
-      <c r="L42" s="23" t="n"/>
+      <c r="G42" s="76" t="n"/>
+      <c r="H42" s="75" t="n"/>
+      <c r="I42" s="76" t="n"/>
+      <c r="J42" s="75" t="n"/>
+      <c r="K42" s="73" t="n"/>
+      <c r="L42" s="75" t="n"/>
     </row>
     <row r="43" ht="19.95" customHeight="1" s="34">
-      <c r="A43" s="55" t="n">
+      <c r="A43" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="B43" s="47" t="inlineStr">
+      <c r="B43" s="77" t="inlineStr">
         <is>
           <t>Acciones correctivas vencidas</t>
         </is>
@@ -3200,23 +3340,23 @@
       <c r="C43" s="22" t="n"/>
       <c r="D43" s="22" t="n"/>
       <c r="E43" s="23" t="n"/>
-      <c r="F43" s="55" t="inlineStr">
+      <c r="F43" s="69" t="inlineStr">
         <is>
           <t>N°</t>
         </is>
       </c>
-      <c r="G43" s="48" t="n"/>
-      <c r="H43" s="23" t="n"/>
-      <c r="I43" s="48" t="n"/>
-      <c r="J43" s="23" t="n"/>
-      <c r="K43" s="47" t="n"/>
-      <c r="L43" s="23" t="n"/>
+      <c r="G43" s="76" t="n"/>
+      <c r="H43" s="75" t="n"/>
+      <c r="I43" s="76" t="n"/>
+      <c r="J43" s="75" t="n"/>
+      <c r="K43" s="73" t="n"/>
+      <c r="L43" s="75" t="n"/>
     </row>
     <row r="44" ht="19.95" customHeight="1" s="34">
-      <c r="A44" s="55" t="n">
+      <c r="A44" s="69" t="n">
         <v>6</v>
       </c>
-      <c r="B44" s="47" t="inlineStr">
+      <c r="B44" s="77" t="inlineStr">
         <is>
           <t>Contratistas evaluados</t>
         </is>
@@ -3224,17 +3364,17 @@
       <c r="C44" s="22" t="n"/>
       <c r="D44" s="22" t="n"/>
       <c r="E44" s="23" t="n"/>
-      <c r="F44" s="55" t="inlineStr">
+      <c r="F44" s="69" t="inlineStr">
         <is>
           <t>N°</t>
         </is>
       </c>
-      <c r="G44" s="48" t="n"/>
-      <c r="H44" s="23" t="n"/>
-      <c r="I44" s="48" t="n"/>
-      <c r="J44" s="23" t="n"/>
-      <c r="K44" s="47" t="n"/>
-      <c r="L44" s="23" t="n"/>
+      <c r="G44" s="76" t="n"/>
+      <c r="H44" s="75" t="n"/>
+      <c r="I44" s="76" t="n"/>
+      <c r="J44" s="75" t="n"/>
+      <c r="K44" s="73" t="n"/>
+      <c r="L44" s="75" t="n"/>
     </row>
     <row r="45" ht="16.5" customHeight="1" s="34">
       <c r="A45" s="21" t="inlineStr">
@@ -3261,16 +3401,16 @@
         </is>
       </c>
       <c r="B46" s="26" t="n"/>
-      <c r="C46" s="50" t="n"/>
-      <c r="D46" s="25" t="n"/>
-      <c r="E46" s="25" t="n"/>
-      <c r="F46" s="25" t="n"/>
-      <c r="G46" s="25" t="n"/>
-      <c r="H46" s="25" t="n"/>
-      <c r="I46" s="25" t="n"/>
-      <c r="J46" s="25" t="n"/>
-      <c r="K46" s="25" t="n"/>
-      <c r="L46" s="26" t="n"/>
+      <c r="C46" s="78" t="n"/>
+      <c r="D46" s="65" t="n"/>
+      <c r="E46" s="65" t="n"/>
+      <c r="F46" s="65" t="n"/>
+      <c r="G46" s="65" t="n"/>
+      <c r="H46" s="65" t="n"/>
+      <c r="I46" s="65" t="n"/>
+      <c r="J46" s="65" t="n"/>
+      <c r="K46" s="65" t="n"/>
+      <c r="L46" s="66" t="n"/>
     </row>
     <row r="47" ht="43.95" customHeight="1" s="34">
       <c r="A47" s="27" t="inlineStr">
@@ -3279,16 +3419,16 @@
         </is>
       </c>
       <c r="B47" s="26" t="n"/>
-      <c r="C47" s="50" t="n"/>
-      <c r="D47" s="25" t="n"/>
-      <c r="E47" s="25" t="n"/>
-      <c r="F47" s="25" t="n"/>
-      <c r="G47" s="25" t="n"/>
-      <c r="H47" s="25" t="n"/>
-      <c r="I47" s="25" t="n"/>
-      <c r="J47" s="25" t="n"/>
-      <c r="K47" s="25" t="n"/>
-      <c r="L47" s="26" t="n"/>
+      <c r="C47" s="78" t="n"/>
+      <c r="D47" s="65" t="n"/>
+      <c r="E47" s="65" t="n"/>
+      <c r="F47" s="65" t="n"/>
+      <c r="G47" s="65" t="n"/>
+      <c r="H47" s="65" t="n"/>
+      <c r="I47" s="65" t="n"/>
+      <c r="J47" s="65" t="n"/>
+      <c r="K47" s="65" t="n"/>
+      <c r="L47" s="66" t="n"/>
     </row>
     <row r="48" ht="43.95" customHeight="1" s="34">
       <c r="A48" s="27" t="inlineStr">
@@ -3297,16 +3437,16 @@
         </is>
       </c>
       <c r="B48" s="26" t="n"/>
-      <c r="C48" s="50" t="n"/>
-      <c r="D48" s="25" t="n"/>
-      <c r="E48" s="25" t="n"/>
-      <c r="F48" s="25" t="n"/>
-      <c r="G48" s="25" t="n"/>
-      <c r="H48" s="25" t="n"/>
-      <c r="I48" s="25" t="n"/>
-      <c r="J48" s="25" t="n"/>
-      <c r="K48" s="25" t="n"/>
-      <c r="L48" s="26" t="n"/>
+      <c r="C48" s="78" t="n"/>
+      <c r="D48" s="65" t="n"/>
+      <c r="E48" s="65" t="n"/>
+      <c r="F48" s="65" t="n"/>
+      <c r="G48" s="65" t="n"/>
+      <c r="H48" s="65" t="n"/>
+      <c r="I48" s="65" t="n"/>
+      <c r="J48" s="65" t="n"/>
+      <c r="K48" s="65" t="n"/>
+      <c r="L48" s="66" t="n"/>
     </row>
     <row r="49" ht="16.5" customHeight="1" s="34">
       <c r="A49" s="21" t="inlineStr">
@@ -3359,24 +3499,24 @@
         </is>
       </c>
       <c r="B51" s="23" t="n"/>
-      <c r="C51" s="29" t="n"/>
-      <c r="D51" s="23" t="n"/>
+      <c r="C51" s="73" t="n"/>
+      <c r="D51" s="75" t="n"/>
       <c r="E51" s="38" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F51" s="23" t="n"/>
-      <c r="G51" s="29" t="n"/>
-      <c r="H51" s="23" t="n"/>
+      <c r="G51" s="73" t="n"/>
+      <c r="H51" s="75" t="n"/>
       <c r="I51" s="38" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="J51" s="23" t="n"/>
-      <c r="K51" s="29" t="n"/>
-      <c r="L51" s="23" t="n"/>
+      <c r="K51" s="73" t="n"/>
+      <c r="L51" s="75" t="n"/>
     </row>
     <row r="52" ht="21" customHeight="1" s="34">
       <c r="A52" s="38" t="inlineStr">
@@ -3385,24 +3525,24 @@
         </is>
       </c>
       <c r="B52" s="23" t="n"/>
-      <c r="C52" s="29" t="n"/>
-      <c r="D52" s="23" t="n"/>
+      <c r="C52" s="73" t="n"/>
+      <c r="D52" s="75" t="n"/>
       <c r="E52" s="38" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="F52" s="23" t="n"/>
-      <c r="G52" s="29" t="n"/>
-      <c r="H52" s="23" t="n"/>
+      <c r="G52" s="73" t="n"/>
+      <c r="H52" s="75" t="n"/>
       <c r="I52" s="38" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="J52" s="23" t="n"/>
-      <c r="K52" s="29" t="n"/>
-      <c r="L52" s="23" t="n"/>
+      <c r="K52" s="73" t="n"/>
+      <c r="L52" s="75" t="n"/>
     </row>
     <row r="53" ht="21" customHeight="1" s="34">
       <c r="A53" s="38" t="inlineStr">
@@ -3411,24 +3551,24 @@
         </is>
       </c>
       <c r="B53" s="23" t="n"/>
-      <c r="C53" s="29" t="n"/>
-      <c r="D53" s="23" t="n"/>
+      <c r="C53" s="73" t="n"/>
+      <c r="D53" s="75" t="n"/>
       <c r="E53" s="38" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="F53" s="23" t="n"/>
-      <c r="G53" s="29" t="n"/>
-      <c r="H53" s="23" t="n"/>
+      <c r="G53" s="73" t="n"/>
+      <c r="H53" s="75" t="n"/>
       <c r="I53" s="38" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="J53" s="23" t="n"/>
-      <c r="K53" s="29" t="n"/>
-      <c r="L53" s="23" t="n"/>
+      <c r="K53" s="73" t="n"/>
+      <c r="L53" s="75" t="n"/>
     </row>
     <row r="54" ht="16.5" customHeight="1" s="34">
       <c r="A54" s="21" t="inlineStr">
@@ -3469,20 +3609,20 @@
         </is>
       </c>
       <c r="B56" s="63" t="n"/>
-      <c r="C56" s="61" t="n"/>
-      <c r="D56" s="62" t="n"/>
-      <c r="E56" s="62" t="n"/>
-      <c r="F56" s="63" t="n"/>
+      <c r="C56" s="79" t="n"/>
+      <c r="D56" s="80" t="n"/>
+      <c r="E56" s="80" t="n"/>
+      <c r="F56" s="81" t="n"/>
       <c r="G56" s="59" t="inlineStr">
         <is>
           <t>Foto 02</t>
         </is>
       </c>
       <c r="H56" s="63" t="n"/>
-      <c r="I56" s="61" t="n"/>
-      <c r="J56" s="62" t="n"/>
-      <c r="K56" s="62" t="n"/>
-      <c r="L56" s="63" t="n"/>
+      <c r="I56" s="79" t="n"/>
+      <c r="J56" s="80" t="n"/>
+      <c r="K56" s="80" t="n"/>
+      <c r="L56" s="81" t="n"/>
     </row>
     <row r="57" ht="165" customHeight="1" s="34">
       <c r="A57" s="57" t="n"/>
@@ -3505,20 +3645,20 @@
         </is>
       </c>
       <c r="B58" s="63" t="n"/>
-      <c r="C58" s="61" t="n"/>
-      <c r="D58" s="62" t="n"/>
-      <c r="E58" s="62" t="n"/>
-      <c r="F58" s="63" t="n"/>
+      <c r="C58" s="79" t="n"/>
+      <c r="D58" s="80" t="n"/>
+      <c r="E58" s="80" t="n"/>
+      <c r="F58" s="81" t="n"/>
       <c r="G58" s="59" t="inlineStr">
         <is>
           <t>Foto 04</t>
         </is>
       </c>
       <c r="H58" s="63" t="n"/>
-      <c r="I58" s="61" t="n"/>
-      <c r="J58" s="62" t="n"/>
-      <c r="K58" s="62" t="n"/>
-      <c r="L58" s="63" t="n"/>
+      <c r="I58" s="79" t="n"/>
+      <c r="J58" s="80" t="n"/>
+      <c r="K58" s="80" t="n"/>
+      <c r="L58" s="81" t="n"/>
     </row>
     <row r="59" ht="165" customHeight="1" s="34">
       <c r="A59" s="57" t="n"/>
@@ -3541,20 +3681,20 @@
         </is>
       </c>
       <c r="B60" s="63" t="n"/>
-      <c r="C60" s="61" t="n"/>
-      <c r="D60" s="62" t="n"/>
-      <c r="E60" s="62" t="n"/>
-      <c r="F60" s="63" t="n"/>
+      <c r="C60" s="79" t="n"/>
+      <c r="D60" s="80" t="n"/>
+      <c r="E60" s="80" t="n"/>
+      <c r="F60" s="81" t="n"/>
       <c r="G60" s="59" t="inlineStr">
         <is>
           <t>Foto 06</t>
         </is>
       </c>
       <c r="H60" s="63" t="n"/>
-      <c r="I60" s="61" t="n"/>
-      <c r="J60" s="62" t="n"/>
-      <c r="K60" s="62" t="n"/>
-      <c r="L60" s="63" t="n"/>
+      <c r="I60" s="79" t="n"/>
+      <c r="J60" s="80" t="n"/>
+      <c r="K60" s="80" t="n"/>
+      <c r="L60" s="81" t="n"/>
     </row>
     <row r="61" ht="165" customHeight="1" s="34">
       <c r="A61" s="57" t="n"/>
@@ -3577,20 +3717,20 @@
         </is>
       </c>
       <c r="B62" s="63" t="n"/>
-      <c r="C62" s="61" t="n"/>
-      <c r="D62" s="62" t="n"/>
-      <c r="E62" s="62" t="n"/>
-      <c r="F62" s="63" t="n"/>
+      <c r="C62" s="79" t="n"/>
+      <c r="D62" s="80" t="n"/>
+      <c r="E62" s="80" t="n"/>
+      <c r="F62" s="81" t="n"/>
       <c r="G62" s="59" t="inlineStr">
         <is>
           <t>Foto 08</t>
         </is>
       </c>
       <c r="H62" s="63" t="n"/>
-      <c r="I62" s="61" t="n"/>
-      <c r="J62" s="62" t="n"/>
-      <c r="K62" s="62" t="n"/>
-      <c r="L62" s="63" t="n"/>
+      <c r="I62" s="79" t="n"/>
+      <c r="J62" s="80" t="n"/>
+      <c r="K62" s="80" t="n"/>
+      <c r="L62" s="81" t="n"/>
     </row>
     <row r="63" ht="165" customHeight="1" s="34">
       <c r="A63" s="57" t="n"/>
@@ -3613,20 +3753,20 @@
         </is>
       </c>
       <c r="B64" s="63" t="n"/>
-      <c r="C64" s="61" t="n"/>
-      <c r="D64" s="62" t="n"/>
-      <c r="E64" s="62" t="n"/>
-      <c r="F64" s="63" t="n"/>
+      <c r="C64" s="79" t="n"/>
+      <c r="D64" s="80" t="n"/>
+      <c r="E64" s="80" t="n"/>
+      <c r="F64" s="81" t="n"/>
       <c r="G64" s="59" t="inlineStr">
         <is>
           <t>Foto 10</t>
         </is>
       </c>
       <c r="H64" s="63" t="n"/>
-      <c r="I64" s="61" t="n"/>
-      <c r="J64" s="62" t="n"/>
-      <c r="K64" s="62" t="n"/>
-      <c r="L64" s="63" t="n"/>
+      <c r="I64" s="79" t="n"/>
+      <c r="J64" s="80" t="n"/>
+      <c r="K64" s="80" t="n"/>
+      <c r="L64" s="81" t="n"/>
     </row>
     <row r="65" s="34">
       <c r="A65" s="1" t="inlineStr">
@@ -3640,6 +3780,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="180">
     <mergeCell ref="A64:B64"/>
     <mergeCell ref="B16:F16"/>
